--- a/v1/dashboard_hanh_dong_v1.xlsx
+++ b/v1/dashboard_hanh_dong_v1.xlsx
@@ -500,7 +500,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Nhóm Đức·Hùng · Bản này giữ lại để đối chiếu với v2. Các ô tô vàng là chỗ bị nhóm bạn chỉ ra ở chặng 3.</t>
+          <t>Nhóm Đức·Hùng·Vinh · Bản này giữ lại để đối chiếu với v2. Các ô tô vàng là chỗ bị nhóm bạn chỉ ra ở chặng 3.</t>
         </is>
       </c>
     </row>
